--- a/results/feature_selection/global/wrapper/P/metrics_global.xlsx
+++ b/results/feature_selection/global/wrapper/P/metrics_global.xlsx
@@ -488,85 +488,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rf_b</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t, t_ind, I</t>
+          <t>t_ind, t_ind_ad, I, Plag1, X_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7385392853012445</v>
+        <v>0.963144541950247</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07134662053139321</v>
+        <v>0.03616101807160101</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03898020775337301</v>
+        <v>0.005494643481259987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1974340592536481</v>
+        <v>0.07412586243181248</v>
       </c>
       <c r="H2" t="n">
-        <v>37.12963947722649</v>
+        <v>21.79062523500129</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1072243598369878</v>
+        <v>0.01840288785180789</v>
       </c>
       <c r="J2" t="n">
-        <v>-402.8323581519441</v>
+        <v>-641.7016782991551</v>
       </c>
       <c r="K2" t="n">
-        <v>-394.3235124310897</v>
+        <v>-621.8477049504947</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>t_ind, I</t>
+          <t>Plag1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4416449625814676</v>
+        <v>0.9366583320383899</v>
       </c>
       <c r="E3" t="n">
-        <v>0.106819361096532</v>
+        <v>0.0445975032926928</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08324308064327474</v>
+        <v>0.009443374234762179</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2885187700016669</v>
+        <v>0.09717702524137163</v>
       </c>
       <c r="H3" t="n">
-        <v>54.77148121088157</v>
+        <v>27.22097050270869</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2267766676758521</v>
+        <v>0.02611286235281656</v>
       </c>
       <c r="J3" t="n">
-        <v>-309.2347738904668</v>
+        <v>-585.4676822435829</v>
       </c>
       <c r="K3" t="n">
-        <v>-303.5622100765639</v>
+        <v>-582.6314003366314</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tweedie</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -574,116 +574,116 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T, I</t>
+          <t>I, Plag1</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3027258833654658</v>
+        <v>0.9262271470706323</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1415696545810651</v>
+        <v>0.04235893851454542</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1039540106772039</v>
+        <v>0.01099852089465536</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3224189986294292</v>
+        <v>0.1048738332219022</v>
       </c>
       <c r="H4" t="n">
-        <v>117.4228213918994</v>
+        <v>18.22588472713892</v>
       </c>
       <c r="I4" t="n">
-        <v>0.282950042464403</v>
+        <v>0.03083082050506908</v>
       </c>
       <c r="J4" t="n">
-        <v>-281.2396420163099</v>
+        <v>-564.2593043977367</v>
       </c>
       <c r="K4" t="n">
-        <v>-275.5670782024069</v>
+        <v>-558.5867405838338</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ridge_b</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T, I</t>
+          <t>t, t_ind, t_ind_ad, T, I, Plag1, V_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2880096507061369</v>
+        <v>0.9228331498392276</v>
       </c>
       <c r="E5" t="n">
-        <v>0.122043905978378</v>
+        <v>0.04123696102305666</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1061479991969268</v>
+        <v>0.01150451934779565</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3258036206013168</v>
+        <v>0.1072591224455787</v>
       </c>
       <c r="H5" t="n">
-        <v>89.78640630883395</v>
+        <v>23.57664060961761</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2889007042260077</v>
+        <v>0.03470321859168869</v>
       </c>
       <c r="J5" t="n">
-        <v>-278.6080384196301</v>
+        <v>-548.591932089943</v>
       </c>
       <c r="K5" t="n">
-        <v>-272.9354746057272</v>
+        <v>-528.7379587412827</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>Ridge_b</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>t_ind, I</t>
+          <t>t_ind_ad, T, I, Plag1, V_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2877197643832526</v>
+        <v>0.9029955209514944</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1499780229137723</v>
+        <v>0.04826516399532175</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1061912172731257</v>
+        <v>0.01446203782727006</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3258699391983337</v>
+        <v>0.1202582131385215</v>
       </c>
       <c r="H6" t="n">
-        <v>73.34723768247447</v>
+        <v>26.43366267738569</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2890179227762122</v>
+        <v>0.04172477019364073</v>
       </c>
       <c r="J6" t="n">
-        <v>-278.5567480572864</v>
+        <v>-523.7647460936998</v>
       </c>
       <c r="K6" t="n">
-        <v>-272.8841842433835</v>
+        <v>-509.5833365589424</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LASSO_b</t>
+          <t>elasticnet_b</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -691,77 +691,77 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T, I</t>
+          <t>I, Plag1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2853023641921362</v>
+        <v>0.9019331432371529</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1360323758384724</v>
+        <v>0.04598686205418673</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1065516184973836</v>
+        <v>0.01462042377854117</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3264224540337009</v>
+        <v>0.1209149443970478</v>
       </c>
       <c r="H7" t="n">
-        <v>104.6852345960405</v>
+        <v>24.24708394347027</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2899954236905277</v>
+        <v>0.04065435367383296</v>
       </c>
       <c r="J7" t="n">
-        <v>-278.1298420462527</v>
+        <v>-528.3923156963941</v>
       </c>
       <c r="K7" t="n">
-        <v>-272.4572782323497</v>
+        <v>-522.7197518824912</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>elasticnet_b</t>
+          <t>rf_b</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T, I</t>
+          <t>Plag1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.28529017711655</v>
+        <v>0.8979514565668327</v>
       </c>
       <c r="E8" t="n">
-        <v>0.135332448517674</v>
+        <v>0.05520222097278291</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1065534354232602</v>
+        <v>0.01521403866939289</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3264252371114406</v>
+        <v>0.1233452012418517</v>
       </c>
       <c r="H8" t="n">
-        <v>104.0091696404605</v>
+        <v>33.46088432286559</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2900003516613172</v>
+        <v>0.04176439009852521</v>
       </c>
       <c r="J8" t="n">
-        <v>-278.1276935034917</v>
+        <v>-525.3776217697484</v>
       </c>
       <c r="K8" t="n">
-        <v>-272.4551296895888</v>
+        <v>-522.5413398627969</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>poisson</t>
+          <t>LASSO_b</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -769,32 +769,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T, I</t>
+          <t>I, Plag1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2780920078450381</v>
+        <v>0.8720990012788439</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1429375887920894</v>
+        <v>0.04808085071213481</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1076265837697365</v>
+        <v>0.01906828529769292</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3280649078608325</v>
+        <v>0.1380879621751763</v>
       </c>
       <c r="H9" t="n">
-        <v>106.8647574032971</v>
+        <v>22.32156161793993</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2929110062853042</v>
+        <v>0.05271809932473188</v>
       </c>
       <c r="J9" t="n">
-        <v>-276.8650376897094</v>
+        <v>-494.9258262336419</v>
       </c>
       <c r="K9" t="n">
-        <v>-271.1924738758065</v>
+        <v>-489.253262419739</v>
       </c>
     </row>
     <row r="10">
@@ -804,114 +804,114 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I, Plag1</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.2658372433565889</v>
+        <v>0.8509543700876604</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1277680075514533</v>
+        <v>0.04810391195173201</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1094536011336215</v>
+        <v>0.02222065990070131</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3308377262852916</v>
+        <v>0.1490659582221954</v>
       </c>
       <c r="H10" t="n">
-        <v>105.6102754448467</v>
+        <v>24.12440895914042</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2973663477865584</v>
+        <v>0.06126815090419281</v>
       </c>
       <c r="J10" t="n">
-        <v>-276.7440737366789</v>
+        <v>-475.6483323854897</v>
       </c>
       <c r="K10" t="n">
-        <v>-273.9077918297274</v>
+        <v>-469.9757685715867</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>tweedie</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>t, t_ind, t_ind_ad, T, I, FS_calc, mu_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.2583383622734028</v>
+        <v>0.8164868167835393</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1253926258933508</v>
+        <v>0.06417868672171502</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1105715814882504</v>
+        <v>0.02735929952422214</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3325230540703161</v>
+        <v>0.165406467600944</v>
       </c>
       <c r="H11" t="n">
-        <v>81.02484543410064</v>
+        <v>38.89857063470177</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3003985983597545</v>
+        <v>0.07820546463189372</v>
       </c>
       <c r="J11" t="n">
-        <v>-275.4636136064809</v>
+        <v>-437.4360473812894</v>
       </c>
       <c r="K11" t="n">
-        <v>-272.6273316995294</v>
+        <v>-414.7457921256776</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>poisson</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>t_ind_ad, I, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.25831813425966</v>
+        <v>0.8105369517982326</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1253943125606849</v>
+        <v>0.07397529377839844</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1105745972077593</v>
+        <v>0.02824634281674503</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3325275886415431</v>
+        <v>0.1680664833235498</v>
       </c>
       <c r="H12" t="n">
-        <v>81.02502939155974</v>
+        <v>44.48319018077121</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3004067777675336</v>
+        <v>0.07861135443225176</v>
       </c>
       <c r="J12" t="n">
-        <v>-275.4601771405162</v>
+        <v>-441.4157022356354</v>
       </c>
       <c r="K12" t="n">
-        <v>-272.6238952335648</v>
+        <v>-430.0705746078295</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global/wrapper/P/metrics_global.xlsx
+++ b/results/feature_selection/global/wrapper/P/metrics_global.xlsx
@@ -488,397 +488,397 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, I, Plag1, X_calc, V_calc, Xlag1_calc</t>
+          <t>t, t_ind, t_ind_ad, I, X_calc, V_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.963144541950247</v>
+        <v>0.9249436900275416</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03616101807160101</v>
+        <v>0.04812618575066433</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005494643481259987</v>
+        <v>0.01118986674269162</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07412586243181248</v>
+        <v>0.1057821664681322</v>
       </c>
       <c r="H2" t="n">
-        <v>21.79062523500129</v>
+        <v>37.06441366897417</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01840288785180789</v>
+        <v>0.03334979971162166</v>
       </c>
       <c r="J2" t="n">
-        <v>-641.7016782991551</v>
+        <v>-554.0860798323181</v>
       </c>
       <c r="K2" t="n">
-        <v>-621.8477049504947</v>
+        <v>-537.0683883906092</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plag1</t>
+          <t>t, t_ind, t_ind_ad, T, I, V_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9366583320383899</v>
+        <v>0.8988673885198954</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0445975032926928</v>
+        <v>0.0494677292740568</v>
       </c>
       <c r="F3" t="n">
-        <v>0.009443374234762179</v>
+        <v>0.01507748577325522</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09717702524137163</v>
+        <v>0.1227904140120686</v>
       </c>
       <c r="H3" t="n">
-        <v>27.22097050270869</v>
+        <v>30.15667504210073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02611286235281656</v>
+        <v>0.04389402348531003</v>
       </c>
       <c r="J3" t="n">
-        <v>-585.4676822435829</v>
+        <v>-516.5136346829759</v>
       </c>
       <c r="K3" t="n">
-        <v>-582.6314003366314</v>
+        <v>-499.495943241267</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>tweedie</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>I, Plag1</t>
+          <t>t_ind, t_ind_ad, I, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9262271470706323</v>
+        <v>0.8834089358445005</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04235893851454542</v>
+        <v>0.06347623899786929</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01099852089465536</v>
+        <v>0.01738212912102104</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1048738332219022</v>
+        <v>0.1318413027886976</v>
       </c>
       <c r="H4" t="n">
-        <v>18.22588472713892</v>
+        <v>43.37129305454302</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03083082050506908</v>
+        <v>0.04914480963136458</v>
       </c>
       <c r="J4" t="n">
-        <v>-564.2593043977367</v>
+        <v>-502.5913954827537</v>
       </c>
       <c r="K4" t="n">
-        <v>-558.5867405838338</v>
+        <v>-491.2462678549478</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>poisson</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, T, I, Plag1, V_calc</t>
+          <t>t_ind_ad, I, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9228331498392276</v>
+        <v>0.8105369517982326</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04123696102305666</v>
+        <v>0.07397529377839844</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01150451934779565</v>
+        <v>0.02824634281674503</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1072591224455787</v>
+        <v>0.1680664833235498</v>
       </c>
       <c r="H5" t="n">
-        <v>23.57664060961761</v>
+        <v>44.48319018077121</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03470321859168869</v>
+        <v>0.07861135443225176</v>
       </c>
       <c r="J5" t="n">
-        <v>-548.591932089943</v>
+        <v>-441.4157022356354</v>
       </c>
       <c r="K5" t="n">
-        <v>-528.7379587412827</v>
+        <v>-430.0705746078295</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ridge_b</t>
+          <t>rf_b</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>t_ind_ad, T, I, Plag1, V_calc</t>
+          <t>t, t_ind, t_ind_ad, I</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9029955209514944</v>
+        <v>0.8000095840208192</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04826516399532175</v>
+        <v>0.06031964282063969</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01446203782727006</v>
+        <v>0.0298158290148247</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1202582131385215</v>
+        <v>0.1726726064401204</v>
       </c>
       <c r="H6" t="n">
-        <v>26.43366267738569</v>
+        <v>29.5406966433628</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04172477019364073</v>
+        <v>0.08286820510413154</v>
       </c>
       <c r="J6" t="n">
-        <v>-523.7647460936998</v>
+        <v>-434.6021972890204</v>
       </c>
       <c r="K6" t="n">
-        <v>-509.5833365589424</v>
+        <v>-423.2570696612144</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>elasticnet_b</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>I, Plag1</t>
+          <t>t_ind_ad, T, I, X_calc, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9019331432371529</v>
+        <v>0.7270308599634856</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04598686205418673</v>
+        <v>0.1291731487771041</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01462042377854117</v>
+        <v>0.04069595618271882</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1209149443970478</v>
+        <v>0.2017323875403224</v>
       </c>
       <c r="H7" t="n">
-        <v>24.24708394347027</v>
+        <v>57.8625011730297</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04065435367383296</v>
+        <v>0.1143779113388575</v>
       </c>
       <c r="J7" t="n">
-        <v>-528.3923156963941</v>
+        <v>-387.404945068128</v>
       </c>
       <c r="K7" t="n">
-        <v>-522.7197518824912</v>
+        <v>-364.7146898125162</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf_b</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plag1</t>
+          <t>t, t_ind, t_ind_ad, T, I, FS_calc, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8979514565668327</v>
+        <v>0.5308992110887631</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05520222097278291</v>
+        <v>0.1339529016972804</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01521403866939289</v>
+        <v>0.06993649592864906</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1233452012418517</v>
+        <v>0.2644550924611758</v>
       </c>
       <c r="H8" t="n">
-        <v>33.46088432286559</v>
+        <v>55.80206041234009</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04176439009852521</v>
+        <v>0.1956857838234254</v>
       </c>
       <c r="J8" t="n">
-        <v>-525.3776217697484</v>
+        <v>-311.1811238632043</v>
       </c>
       <c r="K8" t="n">
-        <v>-522.5413398627969</v>
+        <v>-277.1457409797866</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LASSO_b</t>
+          <t>Ridge_b</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>I, Plag1</t>
+          <t>t, t_ind, t_ind_ad, T, I, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8720990012788439</v>
+        <v>0.516861070554675</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04808085071213481</v>
+        <v>0.1459121211092655</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01906828529769292</v>
+        <v>0.07202939020961313</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1380879621751763</v>
+        <v>0.2683829171344799</v>
       </c>
       <c r="H9" t="n">
-        <v>22.32156161793993</v>
+        <v>67.92629382474053</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05271809932473188</v>
+        <v>0.2008622519803267</v>
       </c>
       <c r="J9" t="n">
-        <v>-494.9258262336419</v>
+        <v>-309.4658117834276</v>
       </c>
       <c r="K9" t="n">
-        <v>-489.253262419739</v>
+        <v>-278.2667108069614</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>elasticnet_b</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>I, Plag1</t>
+          <t>t, t_ind, t_ind_ad, T, I, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.8509543700876604</v>
+        <v>0.5108324927923402</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04810391195173201</v>
+        <v>0.1457861577915259</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02222065990070131</v>
+        <v>0.072928168497984</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1490659582221954</v>
+        <v>0.2700521588471086</v>
       </c>
       <c r="H10" t="n">
-        <v>24.12440895914042</v>
+        <v>67.71536909157196</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06126815090419281</v>
+        <v>0.2032999701108867</v>
       </c>
       <c r="J10" t="n">
-        <v>-475.6483323854897</v>
+        <v>-307.9033197468449</v>
       </c>
       <c r="K10" t="n">
-        <v>-469.9757685715867</v>
+        <v>-276.7042187703787</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tweedie</t>
+          <t>LASSO_b</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, T, I, FS_calc, mu_calc, dVdt_calc</t>
+          <t>t, t_ind, t_ind_ad, T, I, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.8164868167835393</v>
+        <v>0.4956461030312136</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06417868672171502</v>
+        <v>0.1485383593246743</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02735929952422214</v>
+        <v>0.07519225099540415</v>
       </c>
       <c r="G11" t="n">
-        <v>0.165406467600944</v>
+        <v>0.2742120547959264</v>
       </c>
       <c r="H11" t="n">
-        <v>38.89857063470177</v>
+        <v>68.97062800791251</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07820546463189372</v>
+        <v>0.2089407447874188</v>
       </c>
       <c r="J11" t="n">
-        <v>-437.4360473812894</v>
+        <v>-306.0510944248289</v>
       </c>
       <c r="K11" t="n">
-        <v>-414.7457921256776</v>
+        <v>-277.6882753553141</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>poisson</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -886,32 +886,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>t_ind_ad, I, V_calc, Xlag1_calc</t>
+          <t>t_ind_ad, I, FS_calc, mu_calc</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.8105369517982326</v>
+        <v>0.3699757737612059</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07397529377839844</v>
+        <v>0.1383240005579839</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02824634281674503</v>
+        <v>0.09392797406196014</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1680664833235498</v>
+        <v>0.3064767104723622</v>
       </c>
       <c r="H12" t="n">
-        <v>44.48319018077121</v>
+        <v>77.87884252206648</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07861135443225176</v>
+        <v>0.2567568497150103</v>
       </c>
       <c r="J12" t="n">
-        <v>-441.4157022356354</v>
+        <v>-290.0186049990994</v>
       </c>
       <c r="K12" t="n">
-        <v>-430.0705746078295</v>
+        <v>-278.6734773712935</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global/wrapper/P/metrics_global.xlsx
+++ b/results/feature_selection/global/wrapper/P/metrics_global.xlsx
@@ -492,36 +492,36 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, I, X_calc, V_calc</t>
+          <t>t, t_ind_ad, I, X_calc, V_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9249436900275416</v>
+        <v>0.9386910590244775</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04812618575066433</v>
+        <v>0.04482370269251968</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01118986674269162</v>
+        <v>0.00914032251123701</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1057821664681322</v>
+        <v>0.09560503392205355</v>
       </c>
       <c r="H2" t="n">
-        <v>37.06441366897417</v>
+        <v>42.29957244216249</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03334979971162166</v>
+        <v>0.02729090805052267</v>
       </c>
       <c r="J2" t="n">
-        <v>-554.0860798323181</v>
+        <v>-581.5775106641049</v>
       </c>
       <c r="K2" t="n">
-        <v>-537.0683883906092</v>
+        <v>-567.3961011293476</v>
       </c>
     </row>
     <row r="3">
@@ -531,42 +531,42 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, T, I, V_calc</t>
+          <t>t, t_ind_ad, T, I, V_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8988673885198954</v>
+        <v>0.9011674583865047</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0494677292740568</v>
+        <v>0.04883465232480422</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01507748577325522</v>
+        <v>0.01473457689170108</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1227904140120686</v>
+        <v>0.1213860654758242</v>
       </c>
       <c r="H3" t="n">
-        <v>30.15667504210073</v>
+        <v>31.81187332127793</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04389402348531003</v>
+        <v>0.04246396630823935</v>
       </c>
       <c r="J3" t="n">
-        <v>-516.5136346829759</v>
+        <v>-521.4123555920077</v>
       </c>
       <c r="K3" t="n">
-        <v>-499.495943241267</v>
+        <v>-507.2309460572503</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tweedie</t>
+          <t>poisson</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -574,77 +574,77 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, I, Xlag1_calc</t>
+          <t>t_ind_ad, I, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8834089358445005</v>
+        <v>0.8105369517982326</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06347623899786929</v>
+        <v>0.07397529377839844</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01738212912102104</v>
+        <v>0.02824634281674503</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1318413027886976</v>
+        <v>0.1680664833235498</v>
       </c>
       <c r="H4" t="n">
-        <v>43.37129305454302</v>
+        <v>44.48319018077121</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04914480963136458</v>
+        <v>0.07861135443225176</v>
       </c>
       <c r="J4" t="n">
-        <v>-502.5913954827537</v>
+        <v>-441.4157022356354</v>
       </c>
       <c r="K4" t="n">
-        <v>-491.2462678549478</v>
+        <v>-430.0705746078295</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>poisson</t>
+          <t>rf_b</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>t_ind_ad, I, V_calc, Xlag1_calc</t>
+          <t>t</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8105369517982326</v>
+        <v>0.8021019729577241</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07397529377839844</v>
+        <v>0.08265567727364076</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02824634281674503</v>
+        <v>0.02950388251243948</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1680664833235498</v>
+        <v>0.1717669424320043</v>
       </c>
       <c r="H5" t="n">
-        <v>44.48319018077121</v>
+        <v>45.04569550442939</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07861135443225176</v>
+        <v>0.0805221258713904</v>
       </c>
       <c r="J5" t="n">
-        <v>-441.4157022356354</v>
+        <v>-441.9274101268437</v>
       </c>
       <c r="K5" t="n">
-        <v>-430.0705746078295</v>
+        <v>-439.0911282198922</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rf_b</t>
+          <t>tweedie</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -652,32 +652,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, I</t>
+          <t>t_ind_ad, I, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8000095840208192</v>
+        <v>0.8016498940153284</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06031964282063969</v>
+        <v>0.07482228068122572</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0298158290148247</v>
+        <v>0.02957128128443403</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1726726064401204</v>
+        <v>0.171963023014932</v>
       </c>
       <c r="H6" t="n">
-        <v>29.5406966433628</v>
+        <v>44.73074641064346</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08286820510413154</v>
+        <v>0.08220492869450531</v>
       </c>
       <c r="J6" t="n">
-        <v>-434.6021972890204</v>
+        <v>-435.6399035535175</v>
       </c>
       <c r="K6" t="n">
-        <v>-423.2570696612144</v>
+        <v>-424.2947759257116</v>
       </c>
     </row>
     <row r="7">
@@ -722,157 +722,157 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>Ridge_b</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, T, I, FS_calc, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
+          <t>t_ind_ad, I, FS_calc, X_calc, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.5308992110887631</v>
+        <v>0.491350046590864</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1339529016972804</v>
+        <v>0.1340224453062545</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06993649592864906</v>
+        <v>0.07583273410873911</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2644550924611758</v>
+        <v>0.2753774393604878</v>
       </c>
       <c r="H8" t="n">
-        <v>55.80206041234009</v>
+        <v>71.46529323571744</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1956857838234254</v>
+        <v>0.2091778998988582</v>
       </c>
       <c r="J8" t="n">
-        <v>-311.1811238632043</v>
+        <v>-310.9823791253086</v>
       </c>
       <c r="K8" t="n">
-        <v>-277.1457409797866</v>
+        <v>-291.1284057766482</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ridge_b</t>
+          <t>elasticnet_b</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, T, I, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
+          <t>t_ind_ad, I, FS_calc, X_calc, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.516861070554675</v>
+        <v>0.4907401827316696</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1459121211092655</v>
+        <v>0.1340112122998107</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07202939020961313</v>
+        <v>0.07592365644848739</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2683829171344799</v>
+        <v>0.2755424766682759</v>
       </c>
       <c r="H9" t="n">
-        <v>67.92629382474053</v>
+        <v>71.49873461649288</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2008622519803267</v>
+        <v>0.2094245046944403</v>
       </c>
       <c r="J9" t="n">
-        <v>-309.4658117834276</v>
+        <v>-310.83139746138</v>
       </c>
       <c r="K9" t="n">
-        <v>-278.2667108069614</v>
+        <v>-290.9774241127196</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>elasticnet_b</t>
+          <t>LASSO_b</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, T, I, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
+          <t>t_ind_ad, I, FS_calc, X_calc, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.5108324927923402</v>
+        <v>0.488060765153587</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1457861577915259</v>
+        <v>0.1340652167480741</v>
       </c>
       <c r="F10" t="n">
-        <v>0.072928168497984</v>
+        <v>0.07632312087270134</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2700521588471086</v>
+        <v>0.276266394758214</v>
       </c>
       <c r="H10" t="n">
-        <v>67.71536909157196</v>
+        <v>71.65436604999071</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2032999701108867</v>
+        <v>0.2105079550648149</v>
       </c>
       <c r="J10" t="n">
-        <v>-307.9033197468449</v>
+        <v>-310.1701994532713</v>
       </c>
       <c r="K10" t="n">
-        <v>-276.7042187703787</v>
+        <v>-290.3162261046109</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LASSO_b</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, T, I, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>t_ind_ad, I, FS_calc, X_calc, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.4956461030312136</v>
+        <v>0.4711362084294417</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1485383593246743</v>
+        <v>0.1269385878633877</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07519225099540415</v>
+        <v>0.07884634023282981</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2742120547959264</v>
+        <v>0.2807959049431273</v>
       </c>
       <c r="H11" t="n">
-        <v>68.97062800791251</v>
+        <v>60.01034635053413</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2089407447874188</v>
+        <v>0.2173515756341484</v>
       </c>
       <c r="J11" t="n">
-        <v>-306.0510944248289</v>
+        <v>-306.0720519991186</v>
       </c>
       <c r="K11" t="n">
-        <v>-277.6882753553141</v>
+        <v>-286.2180786504583</v>
       </c>
     </row>
     <row r="12">
